--- a/butce.xlsx
+++ b/butce.xlsx
@@ -621,7 +621,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -676,7 +676,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
